--- a/output/Biblio- Resort 23-24 . Invo_output.xlsx
+++ b/output/Biblio- Resort 23-24 . Invo_output.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,28 +74,38 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -474,13 +484,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="33" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,35 +534,25 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>activity</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>error_type</t>
+          <t>calculations</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>date_check</t>
+          <t>Amount-hotel</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>calculations</t>
+          <t>Total price</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Amount-hotel</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Total price</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -564,37 +562,31 @@
       <c r="A2" s="2" t="n">
         <v>116344159055</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>226041</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>45327</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>45352</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="n">
-        <v>45327</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 03.02 to 17.02:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -602,51 +594,45 @@
 </t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="L2" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>116314162557</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="6" t="n">
         <v>226042</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="7" t="n">
         <v>45335</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="7" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="7" t="n">
         <v>45352</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="I3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="5" t="n">
-        <v>45335</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 03.02 to 17.02:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -654,13 +640,13 @@
 </t>
         </is>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="K3" s="6" t="n">
         <v>228</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="L3" s="6" t="n">
         <v>228</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="M3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -668,37 +654,31 @@
       <c r="A4" s="2" t="n">
         <v>116364160480</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>226048</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>45329</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>45345</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>45352</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
-        <v>45329</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 03.02 to 17.02:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -706,51 +686,45 @@
 </t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>116314164339</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>226061</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="7" t="n">
         <v>45343</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="7" t="n">
         <v>45345</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="7" t="n">
         <v>45352</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>SGL - DLX</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="5" t="n">
-        <v>45343</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  SGL - DLX  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -758,13 +732,13 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="K5" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="L5" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="M5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,39 +746,33 @@
       <c r="A6" s="2" t="n">
         <v>115324150657</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>226091</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>45343</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>45353</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SGL - STD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>30-43</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
-        <v>45343</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  SGL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -813,53 +781,47 @@
 </t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="L6" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>116304165618</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="6" t="n">
         <v>226097</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="7" t="n">
         <v>45343</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="7" t="n">
         <v>45346</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="7" t="n">
         <v>45353</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="5" t="n">
-        <v>45343</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -868,13 +830,13 @@
 </t>
         </is>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="K7" s="6" t="n">
         <v>282</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="L7" s="6" t="n">
         <v>282</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="M7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -882,39 +844,33 @@
       <c r="A8" s="2" t="n">
         <v>116394165662</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>226144</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>45343</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>45347</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>45354</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="n">
-        <v>45343</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -923,53 +879,47 @@
 </t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>298</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="L8" s="3" t="n">
         <v>298</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>116324162923</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="6" t="n">
         <v>226147</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="7" t="n">
         <v>45342</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="7" t="n">
         <v>45347</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="7" t="n">
         <v>45354</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="5" t="n">
-        <v>45342</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -978,13 +928,13 @@
 </t>
         </is>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="K9" s="6" t="n">
         <v>298</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="L9" s="6" t="n">
         <v>298</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="M9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -992,39 +942,33 @@
       <c r="A10" s="2" t="n">
         <v>116314164575</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>226149</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>45347</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>45354</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="3" t="n">
-        <v>45346</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1033,53 +977,47 @@
 </t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>298</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="L10" s="3" t="n">
         <v>298</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="M10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>116324165290</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="6" t="n">
         <v>226187</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="7" t="n">
         <v>45345</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="7" t="n">
         <v>45348</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="7" t="n">
         <v>45355</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>SGL - STD</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>30-43</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="5" t="n">
-        <v>45345</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  SGL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1088,13 +1026,13 @@
 </t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="K11" s="6" t="n">
         <v>249</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="L11" s="6" t="n">
         <v>249</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="M11" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1102,39 +1040,33 @@
       <c r="A12" s="2" t="n">
         <v>116374162287</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>226194</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>45332</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>45348</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>45355</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>SGL - DLX</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>33-91</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="3" t="n">
-        <v>45332</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 03.02 to 17.02:
 first date  second date  SGL - DLX  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1145,53 +1077,47 @@
 </t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>405</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="L12" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="M12" s="8" t="n">
         <v>-153</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>116324164668</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="6" t="n">
         <v>226197</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="7" t="n">
         <v>45341</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="7" t="n">
         <v>45348</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="7" t="n">
         <v>45355</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="5" t="n">
-        <v>45341</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1200,13 +1126,13 @@
 </t>
         </is>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="K13" s="6" t="n">
         <v>314</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="L13" s="6" t="n">
         <v>314</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="M13" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1214,39 +1140,33 @@
       <c r="A14" s="2" t="n">
         <v>116354166603</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>226220</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>45349</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="3" t="n">
-        <v>45349</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1255,53 +1175,47 @@
 </t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="L14" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="M14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>116354165842</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="6" t="n">
         <v>226250</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="7" t="n">
         <v>45343</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="7" t="n">
         <v>45347</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="7" t="n">
         <v>45357</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>38-54</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="5" t="n">
-        <v>45343</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1310,13 +1224,13 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="K15" s="6" t="n">
         <v>460</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="L15" s="6" t="n">
         <v>460</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="M15" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1324,39 +1238,33 @@
       <c r="A16" s="2" t="n">
         <v>116394164177</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>226267</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>45341</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>45351</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>45358</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>DBL- DLX</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>44-60</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
-        <v>45341</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL- DLX  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1365,51 +1273,45 @@
 </t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="L16" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="M16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>116324210792</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="6" t="n">
         <v>226378</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="7" t="n">
         <v>45352</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="7" t="n">
         <v>45353</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="7" t="n">
         <v>45360</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="I17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="5" t="n">
-        <v>45352</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 29.02 to 01.03:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1417,13 +1319,13 @@
 </t>
         </is>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="K17" s="6" t="n">
         <v>308</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="L17" s="6" t="n">
         <v>322</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="M17" s="8" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1431,37 +1333,31 @@
       <c r="A18" s="2" t="n">
         <v>116374209906</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>226436</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>45351</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>45353</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>45360</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
-        <v>45351</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1469,51 +1365,45 @@
 </t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="L18" s="3" t="n">
         <v>378</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="M18" s="8" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>116394212052</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="6" t="n">
         <v>226459</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="7" t="n">
         <v>45353</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="7" t="n">
         <v>45354</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="7" t="n">
         <v>45361</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="I19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="5" t="n">
-        <v>45353</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 02.03 to 14.03:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1521,13 +1411,13 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="K19" s="6" t="n">
         <v>308</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="L19" s="6" t="n">
         <v>308</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="M19" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1535,37 +1425,31 @@
       <c r="A20" s="2" t="n">
         <v>115334200681</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <v>226508</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>45354</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>45355</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>45361</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>DBL - FAM</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
-        <v>45354</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 02.03 to 14.03:
 first date  second date  DBL - FAM  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1573,51 +1457,45 @@
 </t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>444</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="L20" s="3" t="n">
         <v>444</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="M20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>116344209125</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="6" t="n">
         <v>226572</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="7" t="n">
         <v>45348</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="7" t="n">
         <v>45354</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="7" t="n">
         <v>45361</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>SGL - STD</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="I21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="5" t="n">
-        <v>45348</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 18.02 to 28.02 :
 first date  second date  SGL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price     contract name   
@@ -1625,13 +1503,13 @@
 </t>
         </is>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="K21" s="6" t="n">
         <v>301</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="L21" s="6" t="n">
         <v>301</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="M21" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1639,37 +1517,31 @@
       <c r="A22" s="2" t="n">
         <v>116344212231</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="3" t="n">
         <v>226580</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>45354</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
-        <v>45354</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 02.03 to 14.03:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1677,51 +1549,45 @@
 </t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="L22" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>116354211723</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="6" t="n">
         <v>226585</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="7" t="n">
         <v>45354</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="7" t="n">
         <v>45356</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="7" t="n">
         <v>45362</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>DBL - STD</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="I23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="5" t="n">
-        <v>45354</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">spo 02.03 to 14.03:
 first date  second date  DBL - STD  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name   
@@ -1729,13 +1595,13 @@
 </t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="K23" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="L23" s="6" t="n">
         <v>264</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="M23" s="6" t="n">
         <v>0</v>
       </c>
     </row>
